--- a/output/stock_quant_scores/INTC_info.xlsx
+++ b/output/stock_quant_scores/INTC_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FR2"/>
+  <dimension ref="A1:FV2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,235 +1061,255 @@
       </c>
       <c r="DX1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>dividendDate</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1374,7 +1394,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Lip-Bu  Tan', 'age': 65, 'title': 'CEO &amp; Director', 'yearBorn': 1959, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David A. Zinsner', 'age': 55, 'title': 'Executive VP &amp; CFO', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 1614300, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nagasubramaniyan  Chandrasekaran', 'title': 'EVP, Chief Technology &amp; Operations Officer, GM of Intel Foundry Manufacturing and Supply Chain', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Scott C. Gawel', 'age': 53, 'title': 'Corporate VP &amp; Chief Accounting Officer', 'yearBorn': 1971, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John William Pitzer', 'title': 'Corporate Vice President of Corporate Planning &amp; Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Gregory  Ernst', 'title': 'Corporate VP, Chief Revenue Officer &amp; General Manager of Sales and Marketing Group', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James A. Murray', 'title': 'Chief Antitrust Counsel and VP of Law &amp; Policy Group', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Allon  Stabinsky', 'title': 'Senior VP and Chief Deputy General Counsel of the Law &amp; Policy Group', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Rui  Wang', 'age': 63, 'title': 'Senior VP &amp; Chair of Intel China', 'yearBorn': 1961, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Christina S. Min', 'age': 59, 'title': 'Corporate VP &amp; CFO of Data Center Group', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Lip-Bu  Tan', 'age': 65, 'title': 'CEO &amp; Director', 'yearBorn': 1959, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David A. Zinsner', 'age': 55, 'title': 'Executive VP &amp; CFO', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 1614300, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. April  Miller Boise J.D.', 'age': 55, 'title': 'Executive VP and Chief Legal Officer &amp; Corporate Secretary', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 1343100, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nagasubramaniyan  Chandrasekaran', 'title': 'EVP, Chief Technology &amp; Operations Officer, GM of Intel Foundry Manufacturing and Supply Chain', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Scott C. Gawel', 'age': 53, 'title': 'Corporate VP &amp; Chief Accounting Officer', 'yearBorn': 1971, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John William Pitzer', 'title': 'Corporate Vice President of Corporate Planning &amp; Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Gregory  Ernst', 'title': 'Corporate VP, Chief Revenue Officer &amp; General Manager of Sales and Marketing Group', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James A. Murray', 'title': 'Chief Antitrust Counsel and VP of Law &amp; Policy Group', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Allon  Stabinsky', 'title': 'Senior VP and Chief Deputy General Counsel of the Law &amp; Policy Group', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Rui  Wang', 'age': 63, 'title': 'Senior VP &amp; Chair of Intel China', 'yearBorn': 1961, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -1415,28 +1435,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.34</v>
+        <v>33.99</v>
       </c>
       <c r="AD2" t="n">
-        <v>29.375</v>
+        <v>35.02</v>
       </c>
       <c r="AE2" t="n">
-        <v>29.23</v>
+        <v>34.49</v>
       </c>
       <c r="AF2" t="n">
-        <v>31.12</v>
+        <v>36.295</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.34</v>
+        <v>33.99</v>
       </c>
       <c r="AH2" t="n">
-        <v>29.375</v>
+        <v>35.02</v>
       </c>
       <c r="AI2" t="n">
-        <v>29.23</v>
+        <v>34.49</v>
       </c>
       <c r="AJ2" t="n">
-        <v>31.12</v>
+        <v>36.3</v>
       </c>
       <c r="AK2" t="n">
         <v>1722988800</v>
@@ -1451,43 +1471,43 @@
         <v>1.23</v>
       </c>
       <c r="AO2" t="n">
-        <v>31.762783</v>
+        <v>36.59794</v>
       </c>
       <c r="AP2" t="n">
-        <v>106981544</v>
+        <v>265002425</v>
       </c>
       <c r="AQ2" t="n">
-        <v>106981544</v>
+        <v>265002425</v>
       </c>
       <c r="AR2" t="n">
-        <v>106039876</v>
+        <v>114049885</v>
       </c>
       <c r="AS2" t="n">
-        <v>138321750</v>
+        <v>194178450</v>
       </c>
       <c r="AT2" t="n">
-        <v>138321750</v>
+        <v>194178450</v>
       </c>
       <c r="AU2" t="n">
-        <v>30.53</v>
+        <v>35</v>
       </c>
       <c r="AV2" t="n">
-        <v>31.2</v>
+        <v>35.67</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AY2" t="n">
-        <v>143890300928</v>
+        <v>165794299904</v>
       </c>
       <c r="AZ2" t="n">
         <v>17.67</v>
       </c>
       <c r="BA2" t="n">
-        <v>32.38</v>
+        <v>36.3</v>
       </c>
       <c r="BB2" t="n">
         <v>75.828125</v>
@@ -1496,19 +1516,19 @@
         <v>0.216146</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.7113304</v>
+        <v>3.1240683</v>
       </c>
       <c r="BE2" t="n">
-        <v>23.5002</v>
+        <v>24.1462</v>
       </c>
       <c r="BF2" t="n">
-        <v>21.8285</v>
+        <v>22.01365</v>
       </c>
       <c r="BG2" t="n">
         <v>0.125</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.004260395</v>
+        <v>0.003677552</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
@@ -1519,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>165840175104</v>
+        <v>192802504704</v>
       </c>
       <c r="BL2" t="n">
         <v>-0.38636002</v>
@@ -1531,31 +1551,31 @@
         <v>4670261514</v>
       </c>
       <c r="BO2" t="n">
-        <v>107666292</v>
+        <v>101515016</v>
       </c>
       <c r="BP2" t="n">
-        <v>120279305</v>
+        <v>107682899</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BR2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.024600001</v>
+        <v>0.0217</v>
       </c>
       <c r="BT2" t="n">
         <v>0.00077</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.65246004</v>
+        <v>0.65272003</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.024600001</v>
+        <v>0.0217</v>
       </c>
       <c r="BX2" t="n">
         <v>4670261514</v>
@@ -1564,7 +1584,7 @@
         <v>22.363</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.3777176</v>
+        <v>1.5874435</v>
       </c>
       <c r="CA2" t="n">
         <v>1735344000</v>
@@ -1593,16 +1613,16 @@
         <v>965001600</v>
       </c>
       <c r="CI2" t="n">
-        <v>3.125</v>
+        <v>3.633</v>
       </c>
       <c r="CJ2" t="n">
-        <v>18.024</v>
+        <v>20.955</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.24638915</v>
+        <v>0.5132139999999999</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CM2" t="n">
         <v>0.125</v>
@@ -1616,7 +1636,7 @@
         </is>
       </c>
       <c r="CP2" t="n">
-        <v>30.8099</v>
+        <v>35.5</v>
       </c>
       <c r="CQ2" t="n">
         <v>43</v>
@@ -1625,7 +1645,7 @@
         <v>14</v>
       </c>
       <c r="CS2" t="n">
-        <v>24.86528</v>
+        <v>25.13114</v>
       </c>
       <c r="CT2" t="n">
         <v>23</v>
@@ -1639,7 +1659,7 @@
         </is>
       </c>
       <c r="CW2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="CX2" t="n">
         <v>21205999616</v>
@@ -1735,171 +1755,183 @@
       </c>
       <c r="DX2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="EB2" t="n">
+        <v>1758931196</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1758916800</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>NMS</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>finmb_21127</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>4.44248</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1753387200</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1753387200</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1753390800</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1753390800</v>
+      </c>
+      <c r="EQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>0.11833</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>300.00845</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>11.3538</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>0.4702106</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>13.486349</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>0.61263573</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>3.0 - Hold</t>
+        </is>
+      </c>
+      <c r="FC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>322151400000</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>-0.25352156</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>35.41</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>-0.09000015</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>34.49 - 36.3</t>
+        </is>
+      </c>
+      <c r="FK2" t="inlineStr">
+        <is>
           <t>NasdaqGS</t>
         </is>
       </c>
-      <c r="DY2" t="n">
-        <v>106039876</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>13.1399</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.7436276000000001</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>17.67 - 32.38</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>-1.5701008</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.04848983</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>24.638916</v>
-      </c>
-      <c r="EF2" t="n">
+      <c r="FL2" t="n">
+        <v>114049885</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>1.0090549</v>
+      </c>
+      <c r="FO2" t="inlineStr">
+        <is>
+          <t>17.67 - 36.3</t>
+        </is>
+      </c>
+      <c r="FP2" t="n">
+        <v>-0.79999924</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>-0.022038547</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>51.3214</v>
+      </c>
+      <c r="FS2" t="n">
         <v>1725148800</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="FT2" t="n">
         <v>1753387200</v>
       </c>
-      <c r="EH2" t="n">
-        <v>1753387200</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1753387200</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1753390800</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1753390800</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-4.77</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.11781</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>261.52194</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>7.3097</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.31104842</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>8.981400000000001</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>0.4114529</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>3.0 - Hold</t>
-        </is>
-      </c>
-      <c r="EX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1758740034</v>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>NMS</t>
-        </is>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>finmb_21127</t>
-        </is>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="FE2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="FG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>5.009885</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>30.8099</v>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>Intel Corporation</t>
-        </is>
-      </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>Intel Corporation</t>
-        </is>
-      </c>
-      <c r="FL2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="FM2" t="n">
-        <v>1.4699001</v>
-      </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>29.23 - 31.12</t>
-        </is>
-      </c>
-      <c r="FO2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FP2" t="n">
-        <v>322151400000</v>
-      </c>
-      <c r="FQ2" t="inlineStr">
+      <c r="FU2" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="FR2" t="inlineStr"/>
+      <c r="FV2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
